--- a/questionnaire_templates/003_relationship_status_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/003_relationship_status_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'married'}</t>
+          <t>married</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Married'}</t>
+          <t>Married</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'in_a_relationship'}</t>
+          <t>in_a_relationship</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'In a relationship'}</t>
+          <t>In a relationship</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'other,_specify'}</t>
+          <t>other,_specify</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Other, specify'}</t>
+          <t>Other, specify</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'1-2_months'}</t>
+          <t>1-2_months</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': '1-2 months'}</t>
+          <t>1-2 months</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'2-6_months'}</t>
+          <t>2-6_months</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': '2-6 months'}</t>
+          <t>2-6 months</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'6_months_-_1_year'}</t>
+          <t>6_months_-_1_year</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': '6 months - 1 year'}</t>
+          <t>6 months - 1 year</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'over_1_year'}</t>
+          <t>over_1_year</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Over 1 year'}</t>
+          <t>Over 1 year</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'romantic'}</t>
+          <t>romantic</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Romantic'}</t>
+          <t>Romantic</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'family'}</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Family'}</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'friend'}</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Friend'}</t>
+          <t>Friend</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'other,_specify'}</t>
+          <t>other,_specify</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Other, specify'}</t>
+          <t>Other, specify</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'started_dating'}</t>
+          <t>started_dating</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Started dating'}</t>
+          <t>Started dating</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'broke_up'}</t>
+          <t>broke_up</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Broke up'}</t>
+          <t>Broke up</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'got_married'}</t>
+          <t>got_married</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Got married'}</t>
+          <t>Got married</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'moved_in_together'}</t>
+          <t>moved_in_together</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Moved in together'}</t>
+          <t>Moved in together</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_'moved_apart'}</t>
+          <t>moved_apart</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 'Moved apart'}</t>
+          <t>Moved apart</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Somewhat dissatisfied'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Very good'}</t>
+          <t>Very good</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'very_intimate'}</t>
+          <t>very_intimate</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Very intimate'}</t>
+          <t>Very intimate</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'somewhat_intimate'}</t>
+          <t>somewhat_intimate</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Somewhat intimate'}</t>
+          <t>Somewhat intimate</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'somewhat_distant'}</t>
+          <t>somewhat_distant</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Somewhat distant'}</t>
+          <t>Somewhat distant</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_'very_distant'}</t>
+          <t>very_distant</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 'Very distant'}</t>
+          <t>Very distant</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'very_few_conflicts'}</t>
+          <t>very_few_conflicts</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Very few conflicts'}</t>
+          <t>Very few conflicts</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'few_conflicts'}</t>
+          <t>few_conflicts</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Few conflicts'}</t>
+          <t>Few conflicts</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'moderate_conflicts'}</t>
+          <t>moderate_conflicts</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Moderate conflicts'}</t>
+          <t>Moderate conflicts</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'many_conflicts'}</t>
+          <t>many_conflicts</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Many conflicts'}</t>
+          <t>Many conflicts</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'very_much'}</t>
+          <t>very_much</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Very much'}</t>
+          <t>Very much</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'somewhat'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Somewhat'}</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'a_little'}</t>
+          <t>a_little</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'A little'}</t>
+          <t>A little</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'text_messages'}</t>
+          <t>text_messages</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Text messages'}</t>
+          <t>Text messages</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'phone_calls'}</t>
+          <t>phone_calls</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Phone calls'}</t>
+          <t>Phone calls</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'video_calls'}</t>
+          <t>video_calls</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Video calls'}</t>
+          <t>Video calls</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'in-person_meetings'}</t>
+          <t>in-person_meetings</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'In-person meetings'}</t>
+          <t>In-person meetings</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_'other,_specify'}</t>
+          <t>other,_specify</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 'Other, specify'}</t>
+          <t>Other, specify</t>
         </is>
       </c>
     </row>
